--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_662_Saint_Lucia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_662_Saint_Lucia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4175ccb7ec7b4237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rcca8bdc97fc24c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7dd753cfd28f4af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfe74b2de88504911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd8bad41f6cbd4ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8e6f0f10d51646d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4206f4f2a2094dce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra364284fb3234431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rdcc7c658ba074294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8af450f697fa482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R137075acffb34fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R81cc4b8399594437"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ662CommercialTable" displayName="EEZ662CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ662CommercialTable" displayName="EEZ662CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ662FunctionalTable" displayName="EEZ662FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ662FunctionalTable" displayName="EEZ662FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ662ValidationTable" displayName="EEZ662ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ662ValidationTable" displayName="EEZ662ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5518,7 +5472,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d10e2ca012d4d76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f183d80d70b4810"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5528,20 +5482,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5549,444 +5493,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>13.640072116400002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2047444628204858</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>160.23023248297528</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>13.640072116400002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>161.62146313133584</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$73,A2,'Species'!$U$2:$U$73))</x:f>
-        <x:v>2204.528412669505</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2047444628204858</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>160.23023248297528</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2185.551926295321</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>18.976486374183878</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0086826975583922</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.008682697558392256</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>33.7528045985</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>33.7528045985</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$73,A3,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4878.764614088794</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4878.764614088794</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>365.22</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.19</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>15.488166189124811</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>365.22</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>15.488166189124811</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$73,A4,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>5656.588055592164</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.19</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>15.488166189124811</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>5656.588055592164</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>267.1580285893</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.180070147856888</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>151.38057407273723</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>267.1580285893</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>193.03267650341706</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$73,A5,'Species'!$U$2:$U$73))</x:f>
-        <x:v>51570.22930796899</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.180070147856888</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>151.38057407273723</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>40442.535735988975</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>11127.693571980017</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2751482657917939</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.27514826579179386</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>746.1733342953</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.093271962422169</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1239.5725844866395</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>746.1733342953</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1649.7016288554364</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$73,A6,'Species'!$U$2:$U$73))</x:f>
-        <x:v>1230963.3649954486</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.093271962422169</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1239.5725844866395</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>924936.0084674383</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>306027.35652801034</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3308632745686686</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3308632745686685</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5.589830302099999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.108794226984589</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1284.6778226762422</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5.589830302099999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1769.977790485738</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$73,A7,'Species'!$U$2:$U$73))</x:f>
-        <x:v>9893.875487301182</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.108794226984589</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1284.6778226762422</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>7181.131021631508</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2712.7444656696744</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3777600572247122</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3777600572247122</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>23.2489652633</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.435665769419293</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2726.8783848636067</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>23.2489652633</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2747.366018620289</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$73,A8,'Species'!$U$2:$U$73))</x:f>
-        <x:v>63873.41713247392</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.435665769419293</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2726.8783848636067</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>63397.1008469376</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>476.3162855363189</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0075132187304008</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.007513218730400783</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R402059c0a8d34701"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08c8c3ca0394c8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5996,20 +5651,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6017,930 +5662,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.8303087442</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>398.1071705534973</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.8303087442</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$73,A2,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>330.5518648392896</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>330.5518648392896</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.9713699048</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.9713699048</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$73,A3,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2125.1258003809694</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2125.1258003809694</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.32835675470000003</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.046897388683443</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1114.0312888870121</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.32835675470000003</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1117.0266527499132</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$73,A4,'Species'!$U$2:$U$73))</x:f>
-        <x:v>366.7832466103654</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.046897388683443</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1114.0312888870121</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>365.79969865319754</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0.9835479571678434</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0026887609825517</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00268876098255158</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.5061712673000001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.89</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>776.247116628692</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.5061712673000001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>776.247116628692</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$73,A5,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>392.91398676191596</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.89</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>776.247116628692</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>392.91398676191596</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>432.5272142099</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.373496676856876</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2363.1793164625024</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>432.5272142099</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2365.938267728416</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$73,A6,'Species'!$U$2:$U$73))</x:f>
-        <x:v>1023332.6879331685</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.373496676856876</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2363.1793164625024</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1022139.3664279819</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1193.3215051866136</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0011674743624803</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.001167474362480386</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1.1885858125</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3816367711439423</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>240.7890709928864</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1.1885858125</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>240.87599070388464</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$73,A7,'Species'!$U$2:$U$73))</x:f>
-        <x:v>286.30178512251916</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3816367711439423</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>240.7890709928864</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>286.19847358720006</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.10331153531910786</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.00036097863844</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00036097863843997935</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>7.7882272543</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.061570986581221</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1152.3143932675666</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>7.7882272543</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1155.6551679566394</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$73,A8,'Species'!$U$2:$U$73))</x:f>
-        <x:v>9000.505075652543</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.061570986581221</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1152.3143932675666</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>8974.486363168631</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>26.018712483912168</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0028991868092523</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0028991868092521915</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4.401244489600001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.305168011151333</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2019.1473398920211</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4.401244489600001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2182.9220632666625</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$73,A9,'Species'!$U$2:$U$73))</x:f>
-        <x:v>9607.573702178663</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.305168011151333</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2019.1473398920211</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8886.761103390258</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>720.812598788405</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.081110833339879</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.08111083333987884</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13.640072116400002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.2047444628204858</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>160.23023248297528</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13.640072116400002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>161.62146313133584</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$73,A10,'Species'!$U$2:$U$73))</x:f>
-        <x:v>2204.528412669505</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.2047444628204858</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>160.23023248297528</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2185.551926295321</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>18.976486374183878</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0086826975583922</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.008682697558392256</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.7971734906</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.36335457783222</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>230.86312914126506</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.7971734906</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>250.64492943979468</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$73,A11,'Species'!$U$2:$U$73))</x:f>
-        <x:v>199.80749330271183</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.36335457783222</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>230.86312914126506</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>184.03796650838083</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>15.769526794331</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0856862694883824</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.08568626948838232</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>216.1157321789</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.4339337075581855</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>271.6024652360273</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>216.1157321789</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>288.6521458527503</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$73,A12,'Species'!$U$2:$U$73))</x:f>
-        <x:v>62382.26984597777</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.4339337075581855</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>271.6024652360273</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>58697.565636078274</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>3684.7042098994934</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0627743956664994</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.06277439566649935</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>190.9383346631</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.548016983799403</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>353.19698187027757</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>190.9383346631</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>742.0968398467094</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$73,A13,'Species'!$U$2:$U$73))</x:f>
-        <x:v>141694.7347590799</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.548016983799403</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>353.19698187027757</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>67438.84352634392</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>74255.89123273599</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.1010848844661623</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.1010848844661623</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>134.7250304667</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.6736045636982144</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>471.63341134081446</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>134.7250304667</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>718.8292499309865</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$73,A14,'Species'!$U$2:$U$73))</x:f>
-        <x:v>96844.29259730726</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.6736045636982144</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>471.63341134081446</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>63540.82571200488</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>33303.466885302376</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.5241270712509847</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.5241270712509846</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>365.22</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.19</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>15.488166189124811</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>365.22</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>15.488166189124811</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$73,A15,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5656.588055592164</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.19</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>15.488166189124811</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>5656.588055592164</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>33.7528045985</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>33.7528045985</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$73,A16,'Species'!$U$2:$U$73))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4878.764614088794</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>4878.764614088794</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>51.0524092134</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.056028599457853</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>113.77022041018537</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>51.0524092134</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>190.73220995520936</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$73,A17,'Species'!$U$2:$U$73))</x:f>
-        <x:v>9737.338832809473</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.056028599457853</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>113.77022041018537</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>5808.243848679496</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>3929.094984129977</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.6764686687566082</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.6764686687566082</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26631ab5f9604a1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63aa67448e964aa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7115,7 +6156,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7214,7 +6255,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1369040.768005543</x:v>
+        <x:v>1048677.6806679727</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7228,7 +6269,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1369040.7680055427</x:v>
+        <x:v>1251891.6250043544</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7242,7 +6283,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>4.656612873077393e-10</x:v>
+        <x:v>-320363.0873375698</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7256,7 +6297,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.3283064365386963e-10</x:v>
+        <x:v>-117149.14300118806</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7267,9 +6308,9 @@
         <x:v>EEZ_662</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7281,47 +6322,19 @@
         <x:v>EEZ_662</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_662</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_662</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe80b37f0d545ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0b8d7bdd7bc4f13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7368,7 +6381,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
